--- a/premise/data/additional_inventories/lci-synfuels-from-FT.xlsx
+++ b/premise/data/additional_inventories/lci-synfuels-from-FT.xlsx
@@ -3265,8 +3265,12 @@
       <c r="A97" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B97" s="8" t="s">
-        <v>38</v>
+      <c r="B97" s="8" t="inlineStr">
+        <is>
+          <t>APPROVED GTL LIFETIME-OUTPUT REFERENCE ASSUMPTION, 2026-10-18. Van der Giesen et al. (2014), DOI 10.1021/es500191g, SI https://doi.org/10.1021/es500191g.s001, page S10 and Table S22, gives 18000 tonnes fuel/day, 300 operating days/year and 30 years. Adopt that published production calendar as the reference for the existing GTL equipment: 1/(18000*1000*300*30) = 6.172839506172839E-12 plant units/kg fuel, replacing the inconsistent transcribed 6.7E-12. USER-APPROVED OPERATING ASSUMPTION: this uses the published reference output/calendar; it does not establish measured operation, future plant duty or complete catalyst coverage. Existing product-allocation keys, fuel output and construction recipe remain unchanged. No new hardware, metal-content factors, credits or primary/secondary shares. Prior references to the former dose or preserved lifetime allocation are superseded only for this coefficient.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Adapted from van der Giesen et al. 2014. LHV: 45 MJ/kg, Formula: C13H18, Density: 7551 kg/m3. Economic allocation between 3 other co-products. Allocation key for this co-product: 6%.</t>
+        </is>
       </c>
     </row>
     <row r="98" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.2">
@@ -3407,7 +3411,7 @@
         <v>35</v>
       </c>
       <c r="B105" s="9">
-        <v>6.7000000000000001E-12</v>
+        <v>6.172839506172839e-12</v>
       </c>
       <c r="C105" s="8" t="s">
         <v>27</v>
@@ -3522,8 +3526,12 @@
       <c r="A115" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B115" s="8" t="s">
-        <v>40</v>
+      <c r="B115" s="8" t="inlineStr">
+        <is>
+          <t>APPROVED GTL LIFETIME-OUTPUT REFERENCE ASSUMPTION, 2026-10-18. Van der Giesen et al. (2014), DOI 10.1021/es500191g, SI https://doi.org/10.1021/es500191g.s001, page S10 and Table S22, gives 18000 tonnes fuel/day, 300 operating days/year and 30 years. Adopt that published production calendar as the reference for the existing GTL equipment: 1/(18000*1000*300*30) = 6.172839506172839E-12 plant units/kg fuel, replacing the inconsistent transcribed 6.7E-12. USER-APPROVED OPERATING ASSUMPTION: this uses the published reference output/calendar; it does not establish measured operation, future plant duty or complete catalyst coverage. Existing product-allocation keys, fuel output and construction recipe remain unchanged. No new hardware, metal-content factors, credits or primary/secondary shares. Prior references to the former dose or preserved lifetime allocation are superseded only for this coefficient.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Adapted from van der Giesen et al. 2014. LHV: 44.5 MJ/kg, Formula: C13H18, Density: 7551 kg/m3. Economic allocation between 3 other co-products. Allocation key for this co-product: 7%.</t>
+        </is>
       </c>
     </row>
     <row r="116" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.2">
@@ -3661,7 +3669,7 @@
         <v>35</v>
       </c>
       <c r="B123" s="9">
-        <v>6.7000000000000001E-12</v>
+        <v>6.172839506172839e-12</v>
       </c>
       <c r="C123" s="8" t="s">
         <v>27</v>
@@ -3776,8 +3784,12 @@
       <c r="A133" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B133" s="8" t="s">
-        <v>41</v>
+      <c r="B133" s="8" t="inlineStr">
+        <is>
+          <t>APPROVED GTL LIFETIME-OUTPUT REFERENCE ASSUMPTION, 2026-10-18. Van der Giesen et al. (2014), DOI 10.1021/es500191g, SI https://doi.org/10.1021/es500191g.s001, page S10 and Table S22, gives 18000 tonnes fuel/day, 300 operating days/year and 30 years. Adopt that published production calendar as the reference for the existing GTL equipment: 1/(18000*1000*300*30) = 6.172839506172839E-12 plant units/kg fuel, replacing the inconsistent transcribed 6.7E-12. USER-APPROVED OPERATING ASSUMPTION: this uses the published reference output/calendar; it does not establish measured operation, future plant duty or complete catalyst coverage. Existing product-allocation keys, fuel output and construction recipe remain unchanged. No new hardware, metal-content factors, credits or primary/secondary shares. Prior references to the former dose or preserved lifetime allocation are superseded only for this coefficient.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Adapted from van der Giesen et al. 2014. LHV: 43.3 MJ/kg, Formula: C13H18, Density: 7551 kg/m3. Economic allocation between 3 other co-products. Allocation key for this co-product: 16%.</t>
+        </is>
       </c>
     </row>
     <row r="134" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.2">
@@ -3918,7 +3930,7 @@
         <v>35</v>
       </c>
       <c r="B141" s="9">
-        <v>6.7000000000000001E-12</v>
+        <v>6.172839506172839e-12</v>
       </c>
       <c r="C141" s="8" t="s">
         <v>27</v>
@@ -4033,8 +4045,12 @@
       <c r="A151" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B151" s="8" t="s">
-        <v>42</v>
+      <c r="B151" s="8" t="inlineStr">
+        <is>
+          <t>APPROVED GTL LIFETIME-OUTPUT REFERENCE ASSUMPTION, 2026-10-18. Van der Giesen et al. (2014), DOI 10.1021/es500191g, SI https://doi.org/10.1021/es500191g.s001, page S10 and Table S22, gives 18000 tonnes fuel/day, 300 operating days/year and 30 years. Adopt that published production calendar as the reference for the existing GTL equipment: 1/(18000*1000*300*30) = 6.172839506172839E-12 plant units/kg fuel, replacing the inconsistent transcribed 6.7E-12. USER-APPROVED OPERATING ASSUMPTION: this uses the published reference output/calendar; it does not establish measured operation, future plant duty or complete catalyst coverage. Existing product-allocation keys, fuel output and construction recipe remain unchanged. No new hardware, metal-content factors, credits or primary/secondary shares. Prior references to the former dose or preserved lifetime allocation are superseded only for this coefficient.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Adapted from van der Giesen et al. 2014. LHV: 40.2 MJ/kg, Formula: C13H18, Density: 7551 kg/m3. Energy-based allocation between 3 other co-products. Allocation key for this co-product: 21%.</t>
+        </is>
       </c>
     </row>
     <row r="152" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.2">
@@ -4175,7 +4191,7 @@
         <v>35</v>
       </c>
       <c r="B159" s="9">
-        <v>6.7000000000000001E-12</v>
+        <v>6.172839506172839e-12</v>
       </c>
       <c r="C159" s="8" t="s">
         <v>27</v>
@@ -4292,8 +4308,12 @@
       <c r="A169" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B169" s="8" t="s">
-        <v>43</v>
+      <c r="B169" s="8" t="inlineStr">
+        <is>
+          <t>APPROVED GTL LIFETIME-OUTPUT REFERENCE ASSUMPTION, 2026-10-18. Van der Giesen et al. (2014), DOI 10.1021/es500191g, SI https://doi.org/10.1021/es500191g.s001, page S10 and Table S22, gives 18000 tonnes fuel/day, 300 operating days/year and 30 years. Adopt that published production calendar as the reference for the existing GTL equipment: 1/(18000*1000*300*30) = 6.172839506172839E-12 plant units/kg fuel, replacing the inconsistent transcribed 6.7E-12. USER-APPROVED OPERATING ASSUMPTION: this uses the published reference output/calendar; it does not establish measured operation, future plant duty or complete catalyst coverage. Existing product-allocation keys, fuel output and construction recipe remain unchanged. No new hardware, metal-content factors, credits or primary/secondary shares. Prior references to the former dose or preserved lifetime allocation are superseded only for this coefficient.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Adapted from van der Giesen et al. 2014. LHV: 45 MJ/kg, Formula: C13H18, Density: 7551 kg/m3. Energy-based allocation between 3 other co-products. Allocation key for this co-product: 18%.</t>
+        </is>
       </c>
     </row>
     <row r="170" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.2">
@@ -4434,7 +4454,7 @@
         <v>35</v>
       </c>
       <c r="B177" s="9">
-        <v>6.7000000000000001E-12</v>
+        <v>6.172839506172839e-12</v>
       </c>
       <c r="C177" s="8" t="s">
         <v>27</v>
@@ -4549,8 +4569,12 @@
       <c r="A187" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B187" s="8" t="s">
-        <v>44</v>
+      <c r="B187" s="8" t="inlineStr">
+        <is>
+          <t>APPROVED GTL LIFETIME-OUTPUT REFERENCE ASSUMPTION, 2026-10-18. Van der Giesen et al. (2014), DOI 10.1021/es500191g, SI https://doi.org/10.1021/es500191g.s001, page S10 and Table S22, gives 18000 tonnes fuel/day, 300 operating days/year and 30 years. Adopt that published production calendar as the reference for the existing GTL equipment: 1/(18000*1000*300*30) = 6.172839506172839E-12 plant units/kg fuel, replacing the inconsistent transcribed 6.7E-12. USER-APPROVED OPERATING ASSUMPTION: this uses the published reference output/calendar; it does not establish measured operation, future plant duty or complete catalyst coverage. Existing product-allocation keys, fuel output and construction recipe remain unchanged. No new hardware, metal-content factors, credits or primary/secondary shares. Prior references to the former dose or preserved lifetime allocation are superseded only for this coefficient.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Adapted from van der Giesen et al. 2014. LHV: 44.5 MJ/kg, Formula: C13H18, Density: 7551 kg/m3. Energy-based allocation between 3 other co-products. Allocation key for this co-product: 24%.</t>
+        </is>
       </c>
     </row>
     <row r="188" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.2">
@@ -4688,7 +4712,7 @@
         <v>35</v>
       </c>
       <c r="B195" s="9">
-        <v>6.7000000000000001E-12</v>
+        <v>6.172839506172839e-12</v>
       </c>
       <c r="C195" s="8" t="s">
         <v>27</v>
@@ -4803,8 +4827,12 @@
       <c r="A205" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B205" s="8" t="s">
-        <v>45</v>
+      <c r="B205" s="8" t="inlineStr">
+        <is>
+          <t>APPROVED GTL LIFETIME-OUTPUT REFERENCE ASSUMPTION, 2026-10-18. Van der Giesen et al. (2014), DOI 10.1021/es500191g, SI https://doi.org/10.1021/es500191g.s001, page S10 and Table S22, gives 18000 tonnes fuel/day, 300 operating days/year and 30 years. Adopt that published production calendar as the reference for the existing GTL equipment: 1/(18000*1000*300*30) = 6.172839506172839E-12 plant units/kg fuel, replacing the inconsistent transcribed 6.7E-12. USER-APPROVED OPERATING ASSUMPTION: this uses the published reference output/calendar; it does not establish measured operation, future plant duty or complete catalyst coverage. Existing product-allocation keys, fuel output and construction recipe remain unchanged. No new hardware, metal-content factors, credits or primary/secondary shares. Prior references to the former dose or preserved lifetime allocation are superseded only for this coefficient.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Adapted from van der Giesen et al. 2014. LHV: 43.3 MJ/kg, Formula: C13H18, Density: 7551 kg/m3. Energy-based allocation between 3 other co-products. Allocation key for this co-product: 37%. Post corrected to preserve carbon balance.</t>
+        </is>
       </c>
     </row>
     <row r="206" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.2">
@@ -4945,7 +4973,7 @@
         <v>35</v>
       </c>
       <c r="B213" s="9">
-        <v>6.7000000000000001E-12</v>
+        <v>6.172839506172839e-12</v>
       </c>
       <c r="C213" s="8" t="s">
         <v>27</v>
@@ -5060,8 +5088,12 @@
       <c r="A223" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B223" s="8" t="s">
-        <v>112</v>
+      <c r="B223" s="8" t="inlineStr">
+        <is>
+          <t>APPROVED GTL LIFETIME-OUTPUT REFERENCE ASSUMPTION, 2026-10-18. Van der Giesen et al. (2014), DOI 10.1021/es500191g, SI https://doi.org/10.1021/es500191g.s001, page S10 and Table S22, gives 18000 tonnes fuel/day, 300 operating days/year and 30 years. Adopt that published production calendar as the reference for the existing GTL equipment: 1/(18000*1000*300*30) = 6.172839506172839E-12 plant units/kg fuel, replacing the inconsistent transcribed 6.7E-12. USER-APPROVED OPERATING ASSUMPTION: this uses the published reference output/calendar; it does not establish measured operation, future plant duty or complete catalyst coverage. Existing product-allocation keys, fuel output and construction recipe remain unchanged. No new hardware, metal-content factors, credits or primary/secondary shares. Prior references to the former dose or preserved lifetime allocation are superseded only for this coefficient.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Adapted from A.E.M. van den Oever, D. Costa, M. Messagie, Prospective life cycle assessment of alternatively fueled heavy-duty trucks, Applied Energy, 2023, https://doi.org/10.1016/j.apenergy.2023.120834. Energy-based allocation between 3 other co-products (diesel, wax and C5-C10 olefins). Allocation key for this co-product: 11%. Post corrected to preserve carbon balance.</t>
+        </is>
       </c>
     </row>
     <row r="224" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.2">
@@ -5189,7 +5221,7 @@
         <v>35</v>
       </c>
       <c r="B231" s="9">
-        <v>6.7000000000000001E-12</v>
+        <v>6.172839506172839e-12</v>
       </c>
       <c r="C231" s="8" t="s">
         <v>27</v>

--- a/premise/data/additional_inventories/lci-synfuels-from-FT.xlsx
+++ b/premise/data/additional_inventories/lci-synfuels-from-FT.xlsx
@@ -5499,8 +5499,12 @@
       <c r="A256" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B256" s="8" t="s">
-        <v>28</v>
+      <c r="B256" s="8" t="inlineStr">
+        <is>
+          <t>APPROVED RWGS PAIR-LEVEL THROUGHPUT ASSUMPTION, 2026-10-18. Van der Giesen et al. (2014), DOI 10.1021/es500191g, SI https://doi.org/10.1021/es500191g.s001, pages S7-S8 and Table S19, states 2900 kg CO per 30 minutes, 8000 operating hours/year and 30 years, for construction represented by a two-reactor unit. EXPLICIT USER-APPROVED BOUNDARY ASSUMPTION: treat 2900 kg per 30 minutes as total output of the COMPLETE TWO-REACTOR UNIT, not per vessel. Then 1/(2900*2*8000*30) = 7.183908045977011E-10 pair units/kg CO, replacing the inconsistent 1.93E-9. The source duty/parallel-vessel interpretation remains ambiguous: if both vessels each deliver this throughput, the dose would be half this value. This reference accounting assumption is not proof of industrial performance. Keep the corrected two-vessel steel recipe, catalyst/zeolite lifetime quantities, CO output and other material/energy flows unchanged. Historical dose statements are superseded only for this coefficient. No new recovery credit or primary/secondary split.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Adapted from van der Giesen et al. 2014. Density of syngas: 0.470kg/m3 @1 bar. LHV: 23.9 MJ/kg.</t>
+        </is>
       </c>
     </row>
     <row r="257" spans="1:7" s="8" customFormat="1" ht="16" x14ac:dyDescent="0.2">
@@ -5596,7 +5600,7 @@
         <v>46</v>
       </c>
       <c r="B262" s="9">
-        <v>1.9300000000000002E-9</v>
+        <v>7.183908045977011e-10</v>
       </c>
       <c r="C262" s="8" t="s">
         <v>8</v>
